--- a/information_forms/007_dog_bio_update_form--information_forms.xlsx
+++ b/information_forms/007_dog_bio_update_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'labrador'}</t>
+          <t>labrador</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Labrador'}</t>
+          <t>Labrador</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'golden_retriever'}</t>
+          <t>golden_retriever</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Golden Retriever'}</t>
+          <t>Golden Retriever</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'poodle'}</t>
+          <t>poodle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Poodle'}</t>
+          <t>Poodle</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'mixed'}</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Mixed'}</t>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Extra Large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'black'}</t>
+          <t>black</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'white'}</t>
+          <t>white</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'jill'}</t>
+          <t>jill</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Jill'}</t>
+          <t>Jill</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'mary'}</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Mary'}</t>
+          <t>Mary</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'joe'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>updated_by_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'bob'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Bob'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit'}</t>
+          <t>save_draft</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Submit'}</t>
+          <t>Save Draft</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'save_draft'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Save Draft'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancel'}</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cancel'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'continue'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'Continue'}</t>
+          <t>Continue</t>
         </is>
       </c>
     </row>
